--- a/out/policy_events_2026-05-14.xlsx
+++ b/out/policy_events_2026-05-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,32 +471,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>인도 금 할인 온스당 200달러 돌파…관세 인상 '후폭풍' - 한국경제</t>
+          <t>미중 정상 오늘 베이징서 '담판'…관세·이란·타이완 논의 주목 - v.daum.net</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>인도 금 할인 온스당 200달러 돌파…관세 인상 '후폭풍'&amp;nbsp;&amp;nbsp;한국경제</t>
+          <t>미중 정상 오늘 베이징서 '담판'…관세·이란·타이완 논의 주목&amp;nbsp;&amp;nbsp;v.daum.net트럼프, 오늘 시진핑과 담판…무역·관세 등 논의&amp;nbsp;&amp;nbsp;JTBC비공개 전환 뒤 거친 설전…대만·관세 문제 쟁점&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 22:51:34 GMT</t>
+          <t>Wed, 13 May 2026 21:39:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5tN3drVGJ4SFI3TGRYd1VDZmVFdUtYS2NHZ3JaTm11dTdJN0ZiaC14eXl3VjRsa3lERGdzVFgwRnF2ajdicEFTUGJISnBLSWdfRTZXbjZrNFZZd9IBVEFVX3lxTE9HY2pFOVJpOTZMZlZZX1JJb2xFY3NCNWJvWFJIMmNYaTdoZmJPR1ZvSkRRM3NybXE4X1BFekU3SGNqOTZINE14eWVSQUQxV3B4bkI0Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFB6VWZZZDZBdXRyandEMjRTbGc2VjdaaDAzNHg4bzg4UVdaTF9lZ1VseTl0b1RkRlg1aUo1NWpZOTlZSnAxTXVnNi1xSk1FY28?oc=5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2" t="inlineStr"/>
     </row>
@@ -508,22 +508,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미중 정상 오늘 베이징서 '담판'…관세·이란·타이완 논의 주목 - v.daum.net</t>
+          <t>“美는 과소비-中은 지갑 닫아…무역불균형, 관세로 못잡는다” - 서울경제</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>미중 정상 오늘 베이징서 '담판'…관세·이란·타이완 논의 주목&amp;nbsp;&amp;nbsp;v.daum.net트럼프·시진핑 6개월 만의 재회…관세·이란·대만 놓고 ‘담판’&amp;nbsp;&amp;nbsp;매일경제미·중 정상 오늘 베이징서 '담판'‥관세·이란·대만 논의 주목&amp;nbsp;&amp;nbsp;MBC 뉴스</t>
+          <t>“美는 과소비-中은 지갑 닫아…무역불균형, 관세로 못잡는다”&amp;nbsp;&amp;nbsp;서울경제</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 21:39:00 GMT</t>
+          <t>Thu, 14 May 2026 08:46:05 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFB6VWZZZDZBdXRyandEMjRTbGc2VjdaaDAzNHg4bzg4UVdaTF9lZ1VseTl0b1RkRlg1aUo1NWpZOTlZSnAxTXVnNi1xSk1FY28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9NQ1hVMnNOcFl1TkhCMzhuMFlIYjdxYXVnUnlXY2haSlN2Nk1zWjRvMHRuaHJUNFdTY01SUmZXWVdUU05ZT1BtTlNGb1VOUDJSN3fSAVNBVV95cUxPWGVUbVUxZXpxQkZCUWFma29ubXJEYWhBUnhxOWNwbkVldVNsSHhMRkxSQ3dJdUJRZGlaY0FlV3ByMUM3RnJLQ00ybUozZHVmXzFQZw?oc=5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K-푸드 할랄 시장 진출 확대…정부, 관세·통관·외환·인증 애로 지원 - 뉴스1</t>
+          <t>닭·돼지고기 긴급 할당관세 추진…매점매석 제재 강화 - 뉴시스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>K-푸드 할랄 시장 진출 확대…정부, 관세·통관·외환·인증 애로 지원&amp;nbsp;&amp;nbsp;뉴스1</t>
+          <t>닭·돼지고기 긴급 할당관세 추진…매점매석 제재 강화&amp;nbsp;&amp;nbsp;뉴시스닭고기 3만톤·돼지고기 1만2000톤에 일시적 관세 인하 추진...정부, 물가관계차관회의 개최&amp;nbsp;&amp;nbsp;조선일보정부, 고등어 등 생선 4종 8천t 방출…닭·돼지고기 할당관세&amp;nbsp;&amp;nbsp;연합뉴스</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:00:00 GMT</t>
+          <t>Thu, 14 May 2026 01:00:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1nbXItd3ZiOUg2bzBvRUYtTExvTm9acldGbDM0Vm9UME1xd1lneDM1S2dnbjJBNlJKMHY5alY2Z3BZemZFS2x0ZkhYdGJoNlJpOXotQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1JbW9aN1Fsb0xmdHJYSUU1cVhvOHFybHFRLWRnaDRXa2FMalJDWVVjbVhHOTNpNjJxcDF0cVNjSXdId0lLaHhBa1VvRGpoWjBnZGV0WGdKZ0xNNmhrWWJmTtIBeEFVX3lxTE9RZktfcGdKdVlBcDQ2dmpHR0VpQzkxelo0a1dCS0JxTlRvRm12NFJxY0RjUFRRM1RJd3R1eGNBYWVQWTdKSkRCMmttOXFNeXB2bjRnU1FnWEp6clFoLTMtYlRyMzNEdVBzYldiUEhIZWJYT3pTLWVlZg?oc=5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -582,32 +582,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>관세 50% 뚫고 ‘성장 가도’…K철강, 대미 수출 ‘쑥’ - 뉴스토마토</t>
+          <t>인도 금 할인 온스당 200달러 돌파…관세 인상 '후폭풍' - 한국경제</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>관세 50% 뚫고 ‘성장 가도’…K철강, 대미 수출 ‘쑥’&amp;nbsp;&amp;nbsp;뉴스토마토</t>
+          <t>인도 금 할인 온스당 200달러 돌파…관세 인상 '후폭풍'&amp;nbsp;&amp;nbsp;한국경제</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:13:02 GMT</t>
+          <t>Wed, 13 May 2026 22:51:34 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE16RFIzbU4tSzJZYlY3UzlNZndJaWdqRDk1cG1RTEJsbkd6QnJhdjhSYjhIQXV6eV9LMURzbVF3T182ZFlxZFlSQWc0dFYtN0ttMkVzcjNnZENxYXRjUG5V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5tN3drVGJ4SFI3TGRYd1VDZmVFdUtYS2NHZ3JaTm11dTdJN0ZiaC14eXl3VjRsa3lERGdzVFgwRnF2ajdicEFTUGJISnBLSWdfRTZXbjZrNFZZd9IBVEFVX3lxTE9HY2pFOVJpOTZMZlZZX1JJb2xFY3NCNWJvWFJIMmNYaTdoZmJPR1ZvSkRRM3NybXE4X1BFekU3SGNqOTZINE14eWVSQUQxV3B4bkI0Nw?oc=5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -619,22 +619,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>인도, 금 수입관세 15%로 인상…금 구매 부담 커진다 - 디지털투데이</t>
+          <t>"루피화 추락 막아야"…인도, 금·은 수입 관세 2.5배 인상 - 마켓인</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>인도, 금 수입관세 15%로 인상…금 구매 부담 커진다&amp;nbsp;&amp;nbsp;디지털투데이</t>
+          <t>"루피화 추락 막아야"…인도, 금·은 수입 관세 2.5배 인상&amp;nbsp;&amp;nbsp;마켓인</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 13:15:45 GMT</t>
+          <t>Thu, 14 May 2026 06:47:33 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFB0a1dPSTNsamQ5R3RNSklPMHBtcXVnZVlGamZTRE5YTHlRVzBwQUpQeFZvS0VpVWwxb21TczNfNnIzSDZtNjcxM3RVVU1vSmJNSFh6N216RVhQb3BqUGg1U29WUWZLMERjWjJmb3poeEZCbEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9OaTdvR00tXzZrRmMyUllqelNweUdiSnZvbExBUE9mckpCY1lPYTlBdXpkbHotMUl0VW00S2h1bk5iUnA2SHBGLWFDMW9Wb19sWW81QWNmSldrYnE0Q1hSTHdpWWdhbEJPbkFmc2tZaVlPQ1k?oc=5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -656,22 +656,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>미·중 정상회담, ‘관세 휴전’ 넘어 글로벌 질서 재편 분수령 - 뉴스프리존</t>
+          <t>[논현논단] 좌초된 ‘트럼프 관세’, 301條 리스크 대비해야 - 이투데이</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>미·중 정상회담, ‘관세 휴전’ 넘어 글로벌 질서 재편 분수령&amp;nbsp;&amp;nbsp;뉴스프리존</t>
+          <t>[논현논단] 좌초된 ‘트럼프 관세’, 301條 리스크 대비해야&amp;nbsp;&amp;nbsp;이투데이</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 23:03:50 GMT</t>
+          <t>Wed, 13 May 2026 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBCVmNmWGE4bTV6a2tOdE04TnNMVE5nTjhWZms4RlVNRUJsNFNONWZud014a2c3aV9lR3B0Z2RiOTNHLTNWYlRpMlhpUWhRZ2pySkxha3k5bDhWR1FrMUp2MGRqdnB4SGdycGJKcnoxdW5uRWPSAXdBVV95cUxQWEJ3TEpTT0VCWlRwTjlMTjdteGhNWGEyclc1dWQ0aE00aUprSWdtc2twaHRMQWFpTlJWN1FKMWIwN1V1QlJCb1RQbVh5RHFUbE9ydnp3clIwUlpkNnQ2M1BlUVBQLXFqNlVOQmowVWM4a2oxLWNvMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFBwc0dPUHlIaEF1UmhSWC1UZ1h3eFJ0NmwwbGxlM3lFbC1Ec19GVXB5dlJDNS1VdU1JRHlyV01fZHhoOVBrOVVZMUZ5ZU1nSG91WDZ1MQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>미중 정상 오늘 베이징서 '담판'…관세·이란·대만 논의 - 매일일보</t>
+          <t>EU 철강 규제·멕시코 관세 압박에…정부, 통상 전방위 대응 - 아시아경제</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>미중 정상 오늘 베이징서 '담판'…관세·이란·대만 논의&amp;nbsp;&amp;nbsp;매일일보</t>
+          <t>EU 철강 규제·멕시코 관세 압박에…정부, 통상 전방위 대응&amp;nbsp;&amp;nbsp;아시아경제</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 23:04:06 GMT</t>
+          <t>Thu, 14 May 2026 08:33:21 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBVOEFUcTFsT2tvT0Ywam1kYlZWZi0tdTVNUlJ2TVYzRnRfMjI2TFI4a001Mk96UVBCVzYzMXVmWWM3RV9HY19GUktSekZjUHpZaEFCeU50aFVJbktwUE12WW1iaWI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1KTGJWSDJ3QVFTYXNCaGZDUnQ3dFk4TWNSRExTOUJUUDE5aTZaR01ITFpkQW1ycGF2WVdXRnFvejdUT1NKd2VrenhzSXJpaDBnTjJCd0t0M0NyTG9WZEpwMw?oc=5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -730,22 +730,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>트럼프·시진핑 베이징 담판… '반도체·유가·관세' 3대 고차방정식에 韓 경제 운명은? - 글로벌이코노믹</t>
+          <t>인천공항세관 “관세행정 장벽 낮췄다”…‘면세점 맞춤형 지원’ - 인천일보</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>트럼프·시진핑 베이징 담판… '반도체·유가·관세' 3대 고차방정식에 韓 경제 운명은?&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
+          <t>인천공항세관 “관세행정 장벽 낮췄다”…‘면세점 맞춤형 지원’&amp;nbsp;&amp;nbsp;인천일보</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 20:54:21 GMT</t>
+          <t>Thu, 14 May 2026 09:14:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNbHVXT3dFMGNkZWpYTllUT1MyVldNbnJVN18zOHpmT1FoWFp0Q2E1Y1dsbHJ2ZzNRVkllZU0wZEZCN21oMmVLZWZnakFCSmdYMDVsVUZaY0tjV1o4UzdZZC1WeEt4aDdUeXZiSFVFUjdhNjVSZkRoczVXR1hxcUZzT0dqclFyZTdN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1vTjFxM2ZkaFZjYVhzUzRNNzJqYXNsR2t6RVRac09EZzdIXzRGbmpEemFnYk9feXk3NDk0NTB4azRFSHFRZzl3Y2RUdVg4QXdlaHZMdkFZbE5uX2FVU3pFd2x5VEFyZ0tLY052TnBBVG8?oc=5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -767,22 +767,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>트럼프-시진핑 오늘 담판…靑 '중동·공급망·관세' 파장 촉각 - 뉴스1</t>
+          <t>미중 정상 오늘 베이징서 '담판'…관세·이란·대만 논의 주목 - 연합뉴스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>트럼프-시진핑 오늘 담판…靑 '중동·공급망·관세' 파장 촉각&amp;nbsp;&amp;nbsp;뉴스1</t>
+          <t>미중 정상 오늘 베이징서 '담판'…관세·이란·대만 논의 주목&amp;nbsp;&amp;nbsp;연합뉴스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 20:05:00 GMT</t>
+          <t>Wed, 13 May 2026 21:10:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5LNWZ0ekxoRjIwZm1xaTdqMjNSc3MxM0had0U5em9UajRhZ2NpS1NPdV9vQmg0MU5iWUpVQnZQNk1TWHQ3LUJCSThmSHVMeEdQR2ZqUmZQXzZLRnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA3a1B3czFoY2laMEk1akhwamNvcUphR1dacW91WG8tU2dxSko4Wm85OVIxbDlObW5Yd1MxVVNxUDZBV1RCSnoxOUM2Q1M0aXZjYllMTURveEVrYWvSAWBBVV95cUxQZkFveklhZjZVZnFKTGFtYTJTckhCZXFBMUF2aFBscjduM0xsZFo0V1dsZVU3YmVjdU5kUEstdTJCa1VpZXdPdU9kNFdrR2oxQkZSU2Rvay1aMko3dDhNRHY?oc=5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>관세·이란·대만 등 현안 산적…어떤 카드 꺼낼까? - v.daum.net</t>
+          <t>"미중 회담서 300억불 비민감품목 관세완화 추진…무역委 신설" - 뉴스1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>관세·이란·대만 등 현안 산적…어떤 카드 꺼낼까?&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>"미중 회담서 300억불 비민감품목 관세완화 추진…무역委 신설"&amp;nbsp;&amp;nbsp;뉴스1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 22:15:41 GMT</t>
+          <t>Thu, 14 May 2026 00:41:50 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFAtdUQxYU54R2l4QmlLUkZ2MFNnZGJpd01QUGo4SlladUF0NDNkNkJ4ZEJDV29EZXBGNVBvOWlvYnJ5ZGc3TE0yUWhBLVExczQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ra1VCa0tWa1hHckJwWlZWekdob3JuU1huTHh3YlE2UnZla2J2RlhITzdlNDk0OW91T2FneXNBT2VnTXBIbGwwWkxuYWZrR2JXZHduM1hrTDA?oc=5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -841,22 +841,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>미·중 정상 오늘 베이징서 ‘담판’…관세·이란·대만 현안 논의 - KBS 뉴스</t>
+          <t>돼지고기 할당관세 결국 추진…정부 “연말까지 1만2천톤 적용” - 돼지와사람</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>미·중 정상 오늘 베이징서 ‘담판’…관세·이란·대만 현안 논의&amp;nbsp;&amp;nbsp;KBS 뉴스</t>
+          <t>돼지고기 할당관세 결국 추진…정부 “연말까지 1만2천톤 적용”&amp;nbsp;&amp;nbsp;돼지와사람</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 21:40:00 GMT</t>
+          <t>Thu, 14 May 2026 13:31:50 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1leUEzeE5jcmVLWFZTNTF0X2pHRHR4bnlHYVhhTXpHQ3ZyX0NlaDZER29YdmdjeFdjWTk5b3FxWTJxcTVjRzZQMGtuOTA0cDFXRW9Gb2ZtUW43dVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBOS3BOV0VKVERSSlNTS19GekM5cUoxZjdMYlFiSzM5VXh2ZXdCS3FCM0o5X1FBUTB4aVJzU3JhUEFmRjN4NndqSUNFZFAyZUsxZl92WEl6amVNQndCQmFHTzRKVzQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -878,22 +878,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[논현논단] 좌초된 ‘트럼프 관세’, 301條 리스크 대비해야 - 이투데이</t>
+          <t>미중 LNG 관세 철폐 협상, 호르무즈 위기가 판을 바꾸나 - 글로벌이코노믹</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[논현논단] 좌초된 ‘트럼프 관세’, 301條 리스크 대비해야&amp;nbsp;&amp;nbsp;이투데이</t>
+          <t>미중 LNG 관세 철폐 협상, 호르무즈 위기가 판을 바꾸나&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 21:00:00 GMT</t>
+          <t>Thu, 14 May 2026 04:22:28 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFBwc0dPUHlIaEF1UmhSWC1UZ1h3eFJ0NmwwbGxlM3lFbC1Ec19GVXB5dlJDNS1VdU1JRHlyV01fZHhoOVBrOVVZMUZ5ZU1nSG91WDZ1MQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQNTJlZF9nY3FEdzNMcTR4SDRCNlYxQWFxekNfYjBzVE0ySnhsZ1NmelEtcVp4czluZTJPXzlyRzhlN0pyZVEzZFBKU25penZ4eGZXM0VIaHM3QVNGMWFMOTd2YmZyNi1kQzkxengyallEbTJheklFUW85aFpqZ0JxV09iUmtBZms?oc=5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -915,22 +915,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[월드 프리즘] 미-중 정상회담, 시장은 관세보다 AI 칩 규제 완화 여부에 주목 - 위키리크스한국</t>
+          <t>닭고기 3만t·돼지고기 1만2000t 할당관세 도입…정부, 물가 안정 총력 - 농민신문</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[월드 프리즘] 미-중 정상회담, 시장은 관세보다 AI 칩 규제 완화 여부에 주목&amp;nbsp;&amp;nbsp;위키리크스한국</t>
+          <t>닭고기 3만t·돼지고기 1만2000t 할당관세 도입…정부, 물가 안정 총력&amp;nbsp;&amp;nbsp;농민신문</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 20:33:17 GMT</t>
+          <t>Thu, 14 May 2026 02:17:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9LZzBZd1d3UWJHOWdOeWZWMlhWem8wMnRqQ3hDb3VsVTRIVkJzREUxbTRtSVVfQTR2OFludzByYnNTbkx1Ti1VZ1BBSDh1QXpJWGVDdWZQeVlVVGtfQUMtT2Zma1ktMFBYWGtHS2pCNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFA4dDQtTWpxYzBhZ2tBWnBMV1dxendGQ3hKNzEwQTQ0WWw0VW1kZDR0Y21LdXpGNnZGS0NxNWhBVV9hR21wYVpBa3hLa21JcjZqZGw4clNPdk05dw?oc=5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>美 항소법원, ‘10% 글로벌 관세 무효’ 1심 판결 집행 일시 정지 - 인더스트리뉴스</t>
+          <t>트럼프-시진핑 정상회담…관세·이란 '담판' 주목 - TBS 서울</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>美 항소법원, ‘10% 글로벌 관세 무효’ 1심 판결 집행 일시 정지&amp;nbsp;&amp;nbsp;인더스트리뉴스</t>
+          <t>트럼프-시진핑 정상회담…관세·이란 '담판' 주목&amp;nbsp;&amp;nbsp;TBS 서울</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 09:51:38 GMT</t>
+          <t>Thu, 14 May 2026 02:29:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE0wdEw4NG5nZGt3bHVRNW9fUjVwWG1aUm5MNXJOam5UVk5vdGgxbl9wYVk0TWdvS3g4N1BtMHp3cUhBWFg4bE5SV3kwQ25SYXlvTXRPOEx6d3d2cXRpVWZNc240T2hIM0dGYk5jc25YYzhrdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOcWpnLVdHbGxZZkdjalBJdHRjQ05NTWZQX2N1cmFWakx3LWEtVk1BTDREMmdFYmg1czgxR2lDNjdkRkNrUmFGbFhKcXRWLS1KcEtIZnlaQXpmbmQ3cndBaXVOU0ZJNEo4aXJZbGNXSVlwS3Q4Unh1ODRHcnZUc1RxQ0NoYl8?oc=5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -989,22 +989,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>트럼프·시진핑, 베이징서 정상회담…관세·이란·대만 놓고 '빅딜' - 청년일보</t>
+          <t>미·중 정상회담, ‘관세 휴전’ 넘어 글로벌 질서 재편 분수령 - 뉴스프리존</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>트럼프·시진핑, 베이징서 정상회담…관세·이란·대만 놓고 '빅딜'&amp;nbsp;&amp;nbsp;청년일보</t>
+          <t>미·중 정상회담, ‘관세 휴전’ 넘어 글로벌 질서 재편 분수령&amp;nbsp;&amp;nbsp;뉴스프리존</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 23:53:59 GMT</t>
+          <t>Wed, 13 May 2026 23:03:50 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1RRks1UGI2dmZLU0JBdnV0V2pvc24wSWhjSV9zUHI2NVNYUU55U3FFeGw3a0c3eURmT1o3WU9reHVaSDVfLXB0TUllWk5VdHJDck9hLUxYbTBUQWJRbk1kczQxbDBxUFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBCVmNmWGE4bTV6a2tOdE04TnNMVE5nTjhWZms4RlVNRUJsNFNONWZud014a2c3aV9lR3B0Z2RiOTNHLTNWYlRpMlhpUWhRZ2pySkxha3k5bDhWR1FrMUp2MGRqdnB4SGdycGJKcnoxdW5uRWPSAXdBVV95cUxQWEJ3TEpTT0VCWlRwTjlMTjdteGhNWGEyclc1dWQ0aE00aUprSWdtc2twaHRMQWFpTlJWN1FKMWIwN1V1QlJCb1RQbVh5RHFUbE9ydnp3clIwUlpkNnQ2M1BlUVBQLXFqNlVOQmowVWM4a2oxLWNvMA?oc=5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>美 항소법원 '트럼프 신규 관세 위법' 판결에 효력 정지 인용 - 더구루</t>
+          <t>미중 정상회담 시작…관세·이란·대만문제 논의 결과 주목 - 국제신문</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>美 항소법원 '트럼프 신규 관세 위법' 판결에 효력 정지 인용&amp;nbsp;&amp;nbsp;더구루</t>
+          <t>미중 정상회담 시작…관세·이란·대만문제 논의 결과 주목&amp;nbsp;&amp;nbsp;국제신문</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 04:41:10 GMT</t>
+          <t>Thu, 14 May 2026 04:32:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE50QUN2cWJoSnpTZW5UMHdhNkVzTk1Mc2hENFZJNTM2V0F0RGpFb0I4MWs3Z0lwV1BBd1ZsRjBlRWxZeVJzdThVNXNhcVE0a1JHTFhxMUJocjRabTlrYVZLbDJRdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQWVFlMF9SWjNZalV2QmVTY3Z6ZHVaUzM5aXlpMmR2bHd2SHhpNThuNVQwYWJhSlBXaXhETXBhX1Q0S3lUdTdzN2xTQUNrOFllYllfRHpQRGtuRFNNSnBKSE92NGhrTFFtNmFRZl9EQ0UwODZnOHg3eDRRLUV2Z01WX0VqcjloaWo2Zm5tQVJEeHRjM1lE?oc=5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9년 만에 베이징서 마주한 미중 정상…관세·중동·대만 등 핵심 현안 담판 - 파이낸스스코프</t>
+          <t>닭·돼지고기 할당관세 추진…매점매석에 신고포상·과징금 신설 - 연합인포맥스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9년 만에 베이징서 마주한 미중 정상…관세·중동·대만 등 핵심 현안 담판&amp;nbsp;&amp;nbsp;파이낸스스코프</t>
+          <t>닭·돼지고기 할당관세 추진…매점매석에 신고포상·과징금 신설&amp;nbsp;&amp;nbsp;연합인포맥스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 23:37:00 GMT</t>
+          <t>Thu, 14 May 2026 01:00:17 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1MZ1M4cFItNlg5RDBLNW9YbG9fNTZPR3VwZDZ1UE5mbDhKNDlBMEJtcVNwemRsQl9ZUzVERjlRZDl3N0VTVER5d0RCbmUyZmlZY0pwTVZFaDgtcXJ0NHVrZUdxR2p3TFQ1cnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBDNUp4M3ZZNGtUQ0U3dHhuaGZDY2NCMXc5UXZvMVhYYUFYRHVfTEpPSnoxTWo3eFBpbXRwZXJEWEpsSE1CT0pDczBLc1lpLVlSXzZRel91OGtQTDNMQ2pNeFNtcW9idFZsUzY4MHZRdDk?oc=5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1100,22 +1100,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[뉴스특보] 미·중 정상 오늘 '담판'…이란·관세 논의 주목 - v.daum.net</t>
+          <t>관세부터 이란전까지 테이블에…미·중 ‘관리된 경쟁’ 모색 - v.daum.net</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[뉴스특보] 미·중 정상 오늘 '담판'…이란·관세 논의 주목&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>관세부터 이란전까지 테이블에…미·중 ‘관리된 경쟁’ 모색&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 22:53:20 GMT</t>
+          <t>Thu, 14 May 2026 07:48:03 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1qa1JOR2NaRWE4Y0VrTWQwSVE0TEdGYjdrN015ZlEyTlV6SjFlSzRoNUhGMzg1eUo5VnRBYjRqVXRnYXI0V1lOU1Z5ZHQ4V2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE42QktqSUNZVDV4OTAzeXdXdzBqd2t0aWNYRGVnWmVuemtHdlZVTzFOSWlhdm1uOGhIVkRhLVc4OWF3V2k1TFN1cDZfZExWUFU?oc=5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>日 닛산, 지난해 5조 원 순손실…美 관세 관세 부담만 2.7조 원 - 뉴스1</t>
+          <t>비공개 전환 뒤 거친 설전…대만·관세 문제 쟁점 - v.daum.net</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>日 닛산, 지난해 5조 원 순손실…美 관세 관세 부담만 2.7조 원&amp;nbsp;&amp;nbsp;뉴스1</t>
+          <t>비공개 전환 뒤 거친 설전…대만·관세 문제 쟁점&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 11:57:16 GMT</t>
+          <t>Thu, 14 May 2026 12:14:18 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBHUG0yWlhQaFR5TnR4Y0JJM2tFN2d0MmhWRy1wX3hOd01Hb2hpZ0s0eENMNF8ySThfb0h1Tk1BSnNoUmludGd0d3RJM0FqeDU1TU5kaDhwMENUT1dnXzMwejlUdmVvcXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1WazM4dHF2QUZSZFZaVjN5Vy1JZUZadDJESmQzWmZFNW91b1hZRDJKQmJVWThlMFFMRjJtcEJoamo5a1N3OW8zVzNDcEFLQUU?oc=5</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>관세</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>닛산, 3기 만에 흑자 전환 전망… 구조조정 성과에도 '중동·관세' 리스크 여전 - 글로벌이코노믹</t>
+          <t>이 대통령, 멕시코 대통령과 통화…“FTA 협상 재개 필요성 강조” - 한겨레</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>닛산, 3기 만에 흑자 전환 전망… 구조조정 성과에도 '중동·관세' 리스크 여전&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
+          <t>이 대통령, 멕시코 대통령과 통화…“FTA 협상 재개 필요성 강조”&amp;nbsp;&amp;nbsp;한겨레이 대통령, 멕시코 대통령과 정상통화…"FTA 협상 조속히 재개 필요"(종합)&amp;nbsp;&amp;nbsp;뉴시스李대통령, 멕시코와 FTA 재개 공감…에너지 협력 확대 논의&amp;nbsp;&amp;nbsp;경기일보BTS로 가까워진 한·멕시코 정상…"FTA 협상 재개 논의"&amp;nbsp;&amp;nbsp;이투데이李대통령, 멕시코 대통령과 통화…"FTA 협상 조속 재개 필요"&amp;nbsp;&amp;nbsp;아시아경제李대통령, 멕시코 대통령과 통화…FTA 재개 논의&amp;nbsp;&amp;nbsp;헤럴드경제李, 셰인바움 멕시코 대통령과 통화…“FTA 협상 재개하자” - 조선비즈&amp;nbsp;&amp;nbsp;Chosunbiz李대통령, 멕시코 셰인바움과 첫 통화…“FTA 협상 조속 재개 필요”&amp;nbsp;&amp;nbsp;쿠키뉴스李대통령, 멕시코 정상과 통화…'FTA 협상' 재개 필요성 강조&amp;nbsp;&amp;nbsp;네이트</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 20:53:51 GMT</t>
+          <t>Thu, 14 May 2026 04:54:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNUG53MlRySF81b3JsVTRlLUxwWmZoenltZTQ5NkxSQXhMR2s1SlBISFlaNDN0Z3dsZnB4VjBSR0NYSkxaWWdPaHpmSENfZHFxd1V2Q1p6UllPdDk2X05ydUtsbDEzUUwxWlE2N0Q2T01HMUZjcnZjS1B4cFJGWU5haWZsbVUtdE5G?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE0zSnZBRV9SeFFJZ1JFUXBXZmItejUtdnpXRVlZbEt2Y0hFRnFfSGh4YjMyZDlqTzBmYlZUeWhSY05aTzdPZnNKQU5MekFudTZUdHloWWRGUGdZSE84QkxHZ3NrczVpcXROYzZKQmhtUUc2MWVR?oc=5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1206,27 +1206,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>관세</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>미·중 정상 오늘 베이징서 '담판'‥관세·이란·대만 논의 주목 - v.daum.net</t>
+          <t>EU 철강 TRQ 협의 및 한-멕 FTA 위한 정재계 아웃리치 강화 - 서울Pn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>미·중 정상 오늘 베이징서 '담판'‥관세·이란·대만 논의 주목&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>EU 철강 TRQ 협의 및 한-멕 FTA 위한 정재계 아웃리치 강화&amp;nbsp;&amp;nbsp;서울Pn</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 21:43:09 GMT</t>
+          <t>Thu, 14 May 2026 08:00:58 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1qaHZRMHh2MmdNT0kzZ1FMX290aDA5VlJfbzlsRmRTMXdiNy1KeWdaN05raGNNTWswX2VGMFhOUHhwdjFiaGJjZkRxdTV6QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9tZlM2ZXJhRy1BclItNER3RFhzZWgyMVlYT01aa0hCTVdSYi1waEVZcmp1U18tbmM3alpCVUU0bGZrN2s5anBEd2lhTFdkVGhuTXZRT3V4REg2UUVieUpCR0lB?oc=5</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" t="inlineStr"/>
     </row>
@@ -1248,32 +1248,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>인천FTA통상진흥센터, 화장품 수출기업 원산지관리 지원 - 기호일보</t>
+          <t>이대통령-멕시코 정상 통화…“FTA 협상 재개·에너지 협력 확대” - v.daum.net</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>인천FTA통상진흥센터, 화장품 수출기업 원산지관리 지원&amp;nbsp;&amp;nbsp;기호일보</t>
+          <t>이대통령-멕시코 정상 통화…“FTA 협상 재개·에너지 협력 확대”&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 19:15:59 GMT</t>
+          <t>Thu, 14 May 2026 08:15:02 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE02QW9zMEhIcFZiZHh1VVVRbWRocGtnY1Fob1BlSkJ0anN0Y0xJeGFpQ0tTYng3VFJvaGU4S0hjTmxjV093dnBhMjBVSHI2Q2lyN3BHb0k5NTczQ0Myc2E2VVI0bm5GMlo0WlVqaEJpRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9SdnBPZU9SZE1Vck9TSnYwYWxudzVPRWVkeFhPTmlFdV93cGU2ZTI4TTJhdEt4SVJiTjl0dEVoa3FXUXF2SWhDd0kyQ0Zxd2s?oc=5</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr"/>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>"자유무역협정(FTA), 이젠 어렵지 않아요!" 관세청, 「자유무역협정(FTA) 빈번 민원 사례집」 발간 - 대한민국 정책브리핑</t>
+          <t>李대통령, 멕시코 대통령과 통화…FTA 재개 논의·방문 초청 수락(종합) - 뉴스1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>"자유무역협정(FTA), 이젠 어렵지 않아요!" 관세청, 「자유무역협정(FTA) 빈번 민원 사례집」 발간&amp;nbsp;&amp;nbsp;대한민국 정책브리핑</t>
+          <t>李대통령, 멕시코 대통령과 통화…FTA 재개 논의·방문 초청 수락(종합)&amp;nbsp;&amp;nbsp;뉴스1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:53:17 GMT</t>
+          <t>Thu, 14 May 2026 10:56:16 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQblpET1NrX0xxYUM1ZFRCYXVsUF9jUDdwMVJmNUs4Vm9oeG5kYWhGSmV2ekJ3bnNhRU90VVI4aUN3RkRnem9oUkc1X0FINHRJQmU3WGwzdFpVV2RfVUk3WlhvbDRBOXRNSUhDMi12OXQ1dzgxenpkdTZ1a1lJMG16VGkzd1NEU2kwRjVlbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE14OVpmMS1aakRFLUFIWnZibFY1VWdabktoZER1SWJoSi1VYkZ1WDVDNXBEblY2R2ZxNktLdVRISndkMDVRSFYtbG8wOEZYQWo5Wnpyc1I0MGhobWc?oc=5</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr"/>
     </row>
@@ -1322,32 +1322,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>‘비특혜 원산지판정 대응 전략 및 FTA 원산지증명 완전 정복’교육 개최 - 충청타임즈</t>
+          <t>李대통령, 셰인바움 멕시코 대통령과 통화…FTA 재개 논의·방문 초청 수락 - 중앙일보</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>‘비특혜 원산지판정 대응 전략 및 FTA 원산지증명 완전 정복’교육 개최&amp;nbsp;&amp;nbsp;충청타임즈</t>
+          <t>李대통령, 셰인바움 멕시코 대통령과 통화…FTA 재개 논의·방문 초청 수락&amp;nbsp;&amp;nbsp;중앙일보</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 12:47:00 GMT</t>
+          <t>Thu, 14 May 2026 02:58:01 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1TWDhHWWdoblRNamlxbzNkTzJjODVoNmlWUWtLOXl1X0R0TDAxeG1qaG5iWnZpbmR6dndPU2ZHN3JPbGZEU0JwZC1fRGYtb2lJb1lHZHpBMzNuTTJEeGZqdGo2QXlwMFhI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9rZjJ1U19Qd3BGM2NDV2NWTmIydDBZZmRUTnY0RmwxcFZMNnBsVFlmaWM4VmlSQnNBbGQ2WFhsZGpTVTAzSV9McUplTi1NbEY2YkZhX1VB?oc=5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr"/>
     </row>
@@ -1359,22 +1359,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[FTA 활용 성공 사례] H사-낚시용품 - 한국무역협회-KITA.NET</t>
+          <t>李대통령, 멕시코 대통령과 통화…FTA 재개 논의·방문 초청 수락 - SPN 서울평양뉴스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[FTA 활용 성공 사례] H사-낚시용품&amp;nbsp;&amp;nbsp;한국무역협회-KITA.NET</t>
+          <t>李대통령, 멕시코 대통령과 통화…FTA 재개 논의·방문 초청 수락&amp;nbsp;&amp;nbsp;SPN 서울평양뉴스</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:48:48 GMT</t>
+          <t>Thu, 14 May 2026 05:32:41 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNNlNpSkRTSUlKZEVEOENBOFFPaEd3X0ZMNGhObzJkbVFfWEJPZzJPTWd3SEpPeWRvNVRVX044MzJGRnY1S0RpelJzS2NiV29ZanhsRmF3V052c1hGUlBoZ3B5eTgzNXZJODNoOHQ0Q2I2b0tDRThpcHBJdzNyVGVhcmJscER6d1dJdFQ4Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9fNk9SNWtEOFpsS2tyWkVfRzFJbE5paUFaMmJIeXhIQlItQnRobGtIUnRsXzd4N3pTczJVQl9LWmNzTFk2dmk5cTZ6aUhlZ3ZHRFNmZVVkUU1aTzREc2lzcUU1bTlVdFN5a2kw?oc=5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FTA 잉크도 마르기 전에…EU, 9월부터 브라질산 육류 수입 금지 - 연합뉴스</t>
+          <t>산업부, EU 철강 규제 대응 총력…한-멕 FTA 협의도 본격화 - 페로타임즈</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FTA 잉크도 마르기 전에…EU, 9월부터 브라질산 육류 수입 금지&amp;nbsp;&amp;nbsp;연합뉴스</t>
+          <t>산업부, EU 철강 규제 대응 총력…한-멕 FTA 협의도 본격화&amp;nbsp;&amp;nbsp;페로타임즈</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 08:33:41 GMT</t>
+          <t>Thu, 14 May 2026 08:18:32 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBiTGc5UV9qY0w2NlZkUkJqVGtrZWxTLXFLQVRMTExtV0Nhd01JSFZuaTA3b3VMbnBaT0dkUm1TV2NydWNBdjBkcklTTmk0V21ETWx6ZHpWUERjenlNTUxmcdIBYEFVX3lxTFBiTGc5UV9qY0w2NlZkUkJqVGtrZWxTLXFLQVRMTExtV0Nhd01JSFZuaTA3b3VMbnBaT0dkUm1TV2NydWNBdjBkcklTTmk0V21ETWx6ZHpWUERjenlNTUxmcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScGlRV25fM3pYbWo0U1VPNEF2c3c4VjdfN1B3ZDkxeWpXdmVlX3d1Q0w0WkFleVJjeUZOV1l5SHRZUUJpYWV6WDZWZjQ3U2R6N2tQUGk0YnBRWVNzQjRsRVdVM1JfanMyMU1TNg?oc=5</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="inlineStr"/>
     </row>
@@ -1433,22 +1433,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>인천상의, ‘화장품’ 산업 특화 FTA 교육 마련 - 경기일보</t>
+          <t>李대통령, 멕시코 대통령과 통화…"양국 FTA 협상 조속히 재개" - 연합인포맥스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>인천상의, ‘화장품’ 산업 특화 FTA 교육 마련&amp;nbsp;&amp;nbsp;경기일보</t>
+          <t>李대통령, 멕시코 대통령과 통화…"양국 FTA 협상 조속히 재개"&amp;nbsp;&amp;nbsp;연합인포맥스</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:26:00 GMT</t>
+          <t>Thu, 14 May 2026 05:18:21 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE41LTdUbmxwc3Vmd2NvaEhLLXdpcjFZZmM3Q3FXYnFwWGpTeF81VGduV0Q1RUZGRHl5WEM2TTJWczg2dDc1UDJQeWhaa1NxUW9ORTNxN2VTb1pReGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9kajlnaU93Um10LWZCOEdsTEpyekZ4T3loRGJ3OGdPUHF0a0QtX0dUc05GMVlTczJjRWIyVEF6V2NIVlZLVWd0ZWNSQmZ2dzNLMFd0WTIxX3dxVnVkMnZiZ1JPdjR4V0F2OW9tN053T0s?oc=5</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr"/>
     </row>
@@ -1470,32 +1470,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>복잡한 FTA 원산지…GVC 시대, 통일된 기준 시급 - 동행일보</t>
+          <t>李대통령, 멕시코 대통령과 통화…"FTA 협상 조속 재개 필요" - 신아일보</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>복잡한 FTA 원산지…GVC 시대, 통일된 기준 시급&amp;nbsp;&amp;nbsp;동행일보</t>
+          <t>李대통령, 멕시코 대통령과 통화…"FTA 협상 조속 재개 필요"&amp;nbsp;&amp;nbsp;신아일보</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:20:57 GMT</t>
+          <t>Thu, 14 May 2026 05:35:27 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBMdDFQeHZWNDl4WlRtZVZYVTFlM1lfWmxpYlVuWmpYbXQ4NHBuUzZhYUh5YlA4alR1ekxld0NQN05Ibi1sOWxRRFJZc2lVMWh4OV8zREFQbFhSaGI4UVNBeG1uX1pxazA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5DWHdsSFlsb1NySmZUZ09VRm5aeUNKYUhGcHU1bWpBV3FZRjN4T0xBX1lyMlVSQWlwYVlmVDltVXFxNF9WQ0dtal9tUlMyRG9qekc3XzhaUGE3M29iSnJNTFVQUUJDZW1SeHQ5UXp1UjM?oc=5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr"/>
     </row>
@@ -1507,22 +1507,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>인천상의 FTA통상진흥센터, 화장품·미용 산업 특화 FTA 교육 - 중부일보</t>
+          <t>목포상공회의소, FTA·무역증명 실무역량 강화 지원 - 목포타임즈</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>인천상의 FTA통상진흥센터, 화장품·미용 산업 특화 FTA 교육&amp;nbsp;&amp;nbsp;중부일보</t>
+          <t>목포상공회의소, FTA·무역증명 실무역량 강화 지원&amp;nbsp;&amp;nbsp;목포타임즈</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:52:00 GMT</t>
+          <t>Thu, 14 May 2026 11:48:09 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5YQ3R0bnVmeEU1R2lQektmVUlrR3JWQ3JLcVFCRkpuclpIZkx4VU1LSzJCWjBmNGV0RG5FQTF4WTVEWmkwSFRpdVMxc2dHOFlqcm9CN1VVNDUydjdaOEcwYkVFSnRXbzYzYXdqWHhmdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1waHYxNzFWWVpxZjcxbGxwMmpMSldWSDlNdDlJcHVOLWRGcHp4cXkwTDZPRXVHbVFEY24zREtJcU55WmpfaElmbUNvWDlEX0d1V0dSMGdqYXB3NFF3cnBuNFZzdkc1cWpy?oc=5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1544,22 +1544,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>인천상의, ‘화장품(미용)산업 특화 FTA 교육’ 성황 진행 - 서울일보</t>
+          <t>李대통령, 멕시코 대통령과 정상통화…"FTA 협상 조속히 재개 필요" - 매일일보</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>인천상의, ‘화장품(미용)산업 특화 FTA 교육’ 성황 진행&amp;nbsp;&amp;nbsp;서울일보</t>
+          <t>李대통령, 멕시코 대통령과 정상통화…"FTA 협상 조속히 재개 필요"&amp;nbsp;&amp;nbsp;매일일보</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:51:30 GMT</t>
+          <t>Thu, 14 May 2026 04:43:22 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9PT3BCU2ljbEJFTjhDNnpTeUpMeVBiXzF5VkV3dXNEVlZRRldYWWZKRTkwaEJZbGs3Z3VNd3g1QWNpYnZVRnh5YjNTOHBzSzIzd1BoTEFIc25zdXJvVGdNOFc1TXBYcEM1SDdZ0gFvQVVfeXFMT2wxOTY3Mi0wdFZkVnJuSWV0NDJMLW9WWENKQmlQbnQ5MXltQ2lqOWpKZGdIZVVxWElZZHFUMjc4RkNJd183Y0tCYnpvNmM5YTE1b3NYTE5HZC1jOU5fNnJKQTlITGxjb3E5RmtDNU1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBZU1d4djVYeEVZZElkYl82bU81dTVYZ3BubzJXZjAtY2UzTDByWERRYmExc0NDTUk3OXdla3BHWnJDdWRoVUJYSE9yVUtsY19LanMtN3pYajFLT1VtcXoxOFdMVVY?oc=5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>인천FTA통상진흥센터, 화장품산업 특화 FTA 교육 진행 - 경기신문</t>
+          <t>구미상공회의소 경북FTA통상진흥센터, 수출입·구매 실무 담당자 역량 강화 교육 실시 - 구미일보</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>인천FTA통상진흥센터, 화장품산업 특화 FTA 교육 진행&amp;nbsp;&amp;nbsp;경기신문</t>
+          <t>구미상공회의소 경북FTA통상진흥센터, 수출입·구매 실무 담당자 역량 강화 교육 실시&amp;nbsp;&amp;nbsp;구미일보</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:31:55 GMT</t>
+          <t>Thu, 14 May 2026 11:38:39 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBZYm91N2ZsOWtLaTRYelZJaVdUSVFRZm1KOGlKWnluclUyWllWTXUydUJZck10djdIMWNubzduSWJ6WHZua2xXWkpiYzZ1Z3BCZVFQSTBsdjZfYi1yZXdRSVdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1EUzdQNUx0QW9FTWEwMXJ0WkxqOWRoSE56V1Zfek4zWl9lMVRENWhEa0tKcFNBSkdpOGpuam0wRUZ6WWpDdDlUNXk2Vmc2blBuWHRPMExBYXlIbDBTS0E?oc=5</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1618,32 +1618,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[포토뉴스]한국무역협회 강원지역본부, 2026년 상반기 영동권 FTA 원산지관리 실무과정 - 강원일보</t>
+          <t>李대통령, 멕시코 셰인바움 대통령과 통화…“FTA 협상 재개·문화교류 확대 공감” - 파이낸스투데이</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[포토뉴스]한국무역협회 강원지역본부, 2026년 상반기 영동권 FTA 원산지관리 실무과정&amp;nbsp;&amp;nbsp;강원일보</t>
+          <t>李대통령, 멕시코 셰인바움 대통령과 통화…“FTA 협상 재개·문화교류 확대 공감”&amp;nbsp;&amp;nbsp;파이낸스투데이</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:58:16 GMT</t>
+          <t>Thu, 14 May 2026 08:43:32 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBNNWUtVS1WSk9TNXpEbEZJdGtudDRLaUtBVFE1dXI1WnVVNWZzalJIemRUVlFTNFNhSUNtMDA3bFNrekpPbkhsUEtSSm96Z2x5TVc0YS1WdzgzSVpMMmdKcTN4NEg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5xZ1dNQkZSaUpiek1fUFMtWWh1endQZ1V4SzV2Y0V2RmQ5OVpSRXEzUmhuXzQtZHVLLXNZOERpVXdCbEdVVFRjdUFjcEpsZ3JOWFY5b0VuNnFjUUkweVl0TnRxYjIzWWlnTExlNg?oc=5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I33" t="inlineStr"/>
     </row>
@@ -1655,32 +1655,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>청주상의 충북FTA통상진흥센터, FTA 원산지증명 완전 정복 교육 개최 - gukjenews.com</t>
+          <t>이 대통령, 멕시코 대통령과 통화…“FTA 협상 재개·문화 협력 강화” - KBS 뉴스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>청주상의 충북FTA통상진흥센터, FTA 원산지증명 완전 정복 교육 개최&amp;nbsp;&amp;nbsp;gukjenews.com</t>
+          <t>이 대통령, 멕시코 대통령과 통화…“FTA 협상 재개·문화 협력 강화”&amp;nbsp;&amp;nbsp;KBS 뉴스</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:22:41 GMT</t>
+          <t>Thu, 14 May 2026 02:47:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JOGtuLTNmb0pvcnQ3M1k5aVljdnJ1RWJaNHRXYy13TEtuUjZfelpURGJQalE3TDFxMDBKd2FTUEdZYzNkaTEwWXZFS2lTb1FsZlZnb19tWlF3cm03MDBJRWVBLWstelJaSDl1RDFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE16RWI3VjRsU0FNcmotN0xQamdKT1A0NXJkMnN4MHgwWEtwZEpXSktiYnVERGcwT3MzdGdPV1ZTMVY5cDRodUd4NlV6N3luVHdFQUlucEdfX05YQ3M?oc=5</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I34" t="inlineStr"/>
     </row>
@@ -1692,22 +1692,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>인천FTA통상진흥센터, 화장품 산업 특화 FTA 실무교육 실시 - 세계뉴스통신</t>
+          <t>인천FTA통상진흥센터, 중고차 수출상담회 개최 "중동 전쟁 위기를 시장 다변화 기회로" - 인천뉴스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>인천FTA통상진흥센터, 화장품 산업 특화 FTA 실무교육 실시&amp;nbsp;&amp;nbsp;세계뉴스통신</t>
+          <t>인천FTA통상진흥센터, 중고차 수출상담회 개최 "중동 전쟁 위기를 시장 다변화 기회로"&amp;nbsp;&amp;nbsp;인천뉴스</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 20:41:55 GMT</t>
+          <t>Thu, 14 May 2026 04:21:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9JSnh4R1dKVjJseUFLOElmcmYtVDlGOWxvVUt3WXhNRDQ3UFlJbE12Q0FTQ2lUY2JYUGFfSkdPaGotbVpiZ1ViMFlhY2NyZnhsOUZ4eTEyV0FuQWJicmdWZVEyLVk1VjVwSi1KdXlCRWN6UUVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4tOGlTanRqQ0FWSE9CUlJwQ2Z6NVRPcF9EUXBqb3RXdzktTzVJLUNtbXAtN0tpNDdRV2NJUXdGMU5ZVjdsM2ZIUUhlVGxZdkpicTA4VHFGQjV5czNzWXZEaEp2c2IzTXp2bE1pa05SVQ?oc=5</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1729,59 +1729,59 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>李대통령, 美 베선트·中 허리펑 연쇄 회동…관세·FTA 논의 - 네이트</t>
+          <t>이 대통령, 멕시코 대통령에 "에너지 협력 강화· FTA 협상 재개" - v.daum.net</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>李대통령, 美 베선트·中 허리펑 연쇄 회동…관세·FTA 논의&amp;nbsp;&amp;nbsp;네이트</t>
+          <t>이 대통령, 멕시코 대통령에 "에너지 협력 강화· FTA 협상 재개"&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:05:00 GMT</t>
+          <t>Thu, 14 May 2026 03:23:09 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1LS1FNVnF5b2VEUGthYVhyaWlMMmd0SlhGR2JlZVZraVJrTXVTUjJtY3I0TTF3LUhpbEUzcUNUOF9la3JuVUZDRjRxMVFtZUNOZk9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE4tVjRwcmUyVmNlTTdYVWlNRFlVUHViem54dnZxTi1ucHQzaXRWN3diaTBhM0Y3R3hHRjJuQ0xRUzdIcGxubFhGdG9ibzJlUTQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>화장품 산업 종사업체 체계적 원산지관리 지원 - 현대일보</t>
+          <t>李대통령, 멕시코와 FTA 재개 공감…에너지 협력 확대 논의 - v.daum.net</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>화장품 산업 종사업체 체계적 원산지관리 지원&amp;nbsp;&amp;nbsp;현대일보</t>
+          <t>李대통령, 멕시코와 FTA 재개 공감…에너지 협력 확대 논의&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 04:02:11 GMT</t>
+          <t>Thu, 14 May 2026 05:05:45 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE82Skd3ckRXdXpzZlk5QkY3VUZORTBwcWFqaU01UHJUSGF5WFFRcHNieXRVUDkwenR3ZVllQldYXzlEUk1oMkRkREhEUnh6TFEyOWNNLW9USnB0aWlnRjBCQ1RMM0k2Y094ak9XTFd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9JdkFObjBIbjJhUkxKcHZGTE9ZWDZKNXd3SDBmek5qT2hhT3ltTkp6WGY1TnBEOHNYX1gzMG80Tmk3LXk5UUdsNTIyX0xsWFk?oc=5</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1791,34 +1791,34 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>기상청, 서해·남해서부 해상 짙은 안개 강원산지 오후 한때 소나기 - 정필</t>
+          <t>李, 멕시코 대통령과 통화⋯"FTA 협상 재개·에너지 협력" - 아이뉴스24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>기상청, 서해·남해서부 해상 짙은 안개 강원산지 오후 한때 소나기&amp;nbsp;&amp;nbsp;정필</t>
+          <t>李, 멕시코 대통령과 통화⋯"FTA 협상 재개·에너지 협력"&amp;nbsp;&amp;nbsp;아이뉴스24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:48:00 GMT</t>
+          <t>Thu, 14 May 2026 04:56:26 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiR0FVX3lxTE1fTHNKbTJIMExwbXBtYzZfV3NNVGdKNGttdGYxeEF3cWs3WUh0OTZlYXZ5LTRmd2lVWmY4VnBCeDRfcE5QQ3RJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTEFVX3lxTE5BUnZfODlQdENjc0V4bmk4Z0xGTmxnT1R2TWhZajhtRmVxOURGOVhyZ2JpR1ExN0h2RW4xQ0dQeDV0OW1kdWVrQWU0Sk0?oc=5</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1828,34 +1828,34 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>베트남은 세계무역기구 원산지규제위원회 회의에서 상품 원산지 국가 관리의 최신 동향을 보고했습니다. - Vietnam.vn</t>
+          <t>李대통령, 멕시코 대통령과 통화…FTA 재개·에너지 협력 강화 논의 - 뉴스웍스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>베트남은 세계무역기구 원산지규제위원회 회의에서 상품 원산지 국가 관리의 최신 동향을 보고했습니다.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
+          <t>李대통령, 멕시코 대통령과 통화…FTA 재개·에너지 협력 강화 논의&amp;nbsp;&amp;nbsp;뉴스웍스</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:12:57 GMT</t>
+          <t>Thu, 14 May 2026 03:49:14 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQdFRrcmtoYzJHUmt2ZG1SXzNxRzZ1Y0hrUEMtOHhEOE5lYk40RE1rRlhYMzdSaWtsdWlwbUY1U1Vpb0RsRl8zNEgxWVg0SXYxWlBpdlprRld6UlMtQ0UwX0ltVDRSMFh3anhmdzFTbUlwV3hXVjQ1c19OUGxGR2ZJVEh0OExHS0U4RFNfSm1KOUU3dzNYN0tNUEZmT0kxVGpLOUQ5R0M1eWQ3X3k0bm5MNkhaMG5ydEkyeXFoLTJUTkM5VmpEci1rc25PS3Vfb3VUbWs4dEctRVkzSWk2ckhZbWN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE8tU0thd1pweUV3LW5PRUJGYkVOUDN3dk5KcnBFRi05T0g3WkRGdUpFNEhPcl9JdUVKbzI2QkFtcDlpMjQ3Y1ZpaktSMkk0TlVzRUhGN0x4eHp6ZUI3VDVUTDFBVUJWcXJoY0szYXVUQdIBc0FVX3lxTE80YlVSUlRKQ2pBUlIyVUIxTEdqOFVUYW50a3pzcko0aXRRTUJnUXNQM2s4bmhkcnJTamJ2anRmbHI5VFZQNDNjYTFNeWhnQVlNMWFyZklQbmdDMlBkUWxkdmZISEVhN2ZyZTFGSlV5UzJwNWs?oc=5</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1865,34 +1865,34 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>오늘의 날씨 및 내일날씨늦은 오후 강원산지 소나기, 내일부터 낮 기온 올라 초여름 더위! - 이코노미톡뉴스</t>
+          <t>李대통령, 멕시코 대통령과 통화…FTA 재개 논의·방문 초청 수락 - 뉴스1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>오늘의 날씨 및 내일날씨늦은 오후 강원산지 소나기, 내일부터 낮 기온 올라 초여름 더위!&amp;nbsp;&amp;nbsp;이코노미톡뉴스</t>
+          <t>李대통령, 멕시코 대통령과 통화…FTA 재개 논의·방문 초청 수락&amp;nbsp;&amp;nbsp;뉴스1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 01:50:56 GMT</t>
+          <t>Thu, 14 May 2026 02:39:30 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaOGxxeERfZnljbkVxTkpEd0xlWElHRFpIQXJCZnlqSWdmbXdlMkNwYVIwZjR0akhNbjB3SmdUQVVlX1R5NEZ3UFpHYXlVMFNQNXl5TnAybVU0bWlsYWFTYkRUVWpCLXRTUWFqWA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE4wMnJUc0RRbmU1OGpRMy16X1NkZ1Buaml2M1VMXy04Uy1PTm8yY21YNlhIYnkyeEdHWkdLVy1uTEZaX2YxNjhiNDVBQUcwdEp2QVpaVUkxRk8tUzg?oc=5</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1902,34 +1902,34 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[오늘 날씨] 전국 내륙·서해안 짙은 안개…강원산지 늦은 오후 소나기 5mm, 낮 최고 28도 - ppss.kr</t>
+          <t>李대통령, 멕시코 대통령과 통화⋯“FTA 협상 조속히 재개되길” - 강원일보</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[오늘 날씨] 전국 내륙·서해안 짙은 안개…강원산지 늦은 오후 소나기 5mm, 낮 최고 28도&amp;nbsp;&amp;nbsp;ppss.kr</t>
+          <t>李대통령, 멕시코 대통령과 통화⋯“FTA 협상 조속히 재개되길”&amp;nbsp;&amp;nbsp;강원일보</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 02:16:00 GMT</t>
+          <t>Thu, 14 May 2026 06:14:38 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE8wV0sta0ZjamNBVXFtOG9DX1FOcUpIRHNUbG1EeGNEU1RWcW9fMmtyVkppZEw2R2ROR2RKcVZwM2NOVk9qaDZpWi1YOVNzMTNhRlBfZHV3aUg0Q2thclVuN21JUnA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5mZnExeWdwbkxNNXd6NkxwM1RHem1TRkxBQjZpWjdhSkhMRi0xNGNLR09xc250M1FhNjhoWkVSbnVCeVpKOGVmYmJ5czI3dDlyaEhxVkttNTNEV2tycFVFM1RPSEc?oc=5</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1939,34 +1939,34 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>베트남, 상품 원산지 국가 관리 관련 새로운 사항들을 발표. - Vietnam.vn</t>
+          <t>李대통령, 멕시코 정상과 통화…'FTA 협상' 재개 필요성 강조 - 뉴스핌</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>베트남, 상품 원산지 국가 관리 관련 새로운 사항들을 발표.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
+          <t>李대통령, 멕시코 정상과 통화…'FTA 협상' 재개 필요성 강조&amp;nbsp;&amp;nbsp;뉴스핌</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 00:54:26 GMT</t>
+          <t>Thu, 14 May 2026 04:18:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYTBCUU8wNlYyVktPN0kyd0dGM3pjWW9LMkJkWVdxeUtvYXN1Y2wxODlJNmloY010YVkxOVA4d3dPOE02QVFjUzFDRHRHWFhneFdqMmdTUDRSWVVJcVFmaG91VDFoX2VHanN2MU1obTJwMGZXQlZxYi0xQkNtMERpRWdXVktVa0JsZ3R6LXRKcFFUNDBnMHlCNmFKNzVtbFJa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFAtWERTTDdLdWpmaW5IMnk5U3p6dFNJbFplT1ZqVDlJRlpkQWJQQVZGUU5pazRvWXJEb1dDV3ZycGhJZVBYRUNjc2tGLV9UUFdyeGViWER6Tjg3SXZS?oc=5</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1976,34 +1976,34 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>반도체 수출규제 완화카드 꺼낼까…미·중 회담 증시 영향은? [분석+] - 한국경제</t>
+          <t>창원상의 경남FTA센터, 탄소국경세 대응 지원 본격화…도내 기업 9곳과 협약 - 쿠키뉴스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>반도체 수출규제 완화카드 꺼낼까…미·중 회담 증시 영향은? [분석+]&amp;nbsp;&amp;nbsp;한국경제</t>
+          <t>창원상의 경남FTA센터, 탄소국경세 대응 지원 본격화…도내 기업 9곳과 협약&amp;nbsp;&amp;nbsp;쿠키뉴스</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 13:00:01 GMT</t>
+          <t>Thu, 14 May 2026 08:49:23 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBPVWdqUHBpRkFXSW1lRUR0X1poTGdnc3JvSXFhU01DNm5RaU5aSWZUWnA1Zi1ZM2hqTXJvekdXV0dRUnR3ODV6QVE3ZF9oRWRFNnh2MDgxYWRfUdIBVEFVX3lxTE5UWDlqZXlxYjNpdmFYTE5ybUVIeThjNVhtVEYxRFRCLW93MVRPdG9XQ1IwMTdmU1JGell5eEJjaktaUWFIWmpsZFc4Y0tYRU1XS1J2Wg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1GcUU1STdNUDFjMG5UeVBoSDFNYU50OXBCSGNPOUFjTUpoa0lxR2FBOG1jMXRqdEVjZGNsZTJ0NEUyTmRiVmZmazVBZkU1aGR5WEZvR01RQm5tMHpXb2RKS3hxaw?oc=5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2013,34 +2013,34 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>희토류 카드 쥔 중국…미·중 정상회담에 반도체株 촉각 - newsis.com</t>
+          <t>충남경제진흥원, 6월 FTA 활용 교육 실시 - hdnews.co.kr</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>희토류 카드 쥔 중국…미·중 정상회담에 반도체株 촉각&amp;nbsp;&amp;nbsp;newsis.com</t>
+          <t>충남경제진흥원, 6월 FTA 활용 교육 실시&amp;nbsp;&amp;nbsp;hdnews.co.kr</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 21:00:00 GMT</t>
+          <t>Thu, 14 May 2026 05:27:59 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBSeVdmU2dhNWxzRnRObGkxczAzMkJaWTB5RTg5NTdNUFA5MHJmc0hyb1NKYVBSZ1Q1Vm4tSWU0TVZydmNlTDBZT1hQdnlreFRpVC1kVjRfbzN2T3l6ZGo1dtIBeEFVX3lxTE9veXFVZDIxT1dNa0pOUEwtcmlBaGlnLVBUT2J1UElzUFkySzBEMDJLRVF6OV92Y19YUHVuS0RrVy0yZzFQMXA0aFlEQjdweFNULXI1N2h1YnVlaEdNU2tZQS1CWUh4WUJESkpwSU51X0d2alRaTVZGWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE4tZldTMGF5UnprT0VrcGhqN0IwWVJ6azdjcVNlRGZ2ZTh3UGl5UE9KYm5LcnV2VWFxeUE0dDVmdG1ocGVRNzVPNGxmRGdjVGlPd3lfYmhKTFlKNDRFQmVGT2VFQVppUXR6Tks4?oc=5</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2050,34 +2050,34 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>미중 회담서 논의될 반도체, 삼전닉스에 득일까 실일까 - nocutnews.co.kr</t>
+          <t>李 대통령, 멕시코 대통령과 통화...“FTA 협상 재개・에너지 협력 강화” - ksdaily.co.kr</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>미중 회담서 논의될 반도체, 삼전닉스에 득일까 실일까&amp;nbsp;&amp;nbsp;nocutnews.co.kr</t>
+          <t>李 대통령, 멕시코 대통령과 통화...“FTA 협상 재개・에너지 협력 강화”&amp;nbsp;&amp;nbsp;ksdaily.co.kr</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 20:00:00 GMT</t>
+          <t>Thu, 14 May 2026 05:38:14 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE44b0ZmRzRvY0hmSDdiX2UtUFJtdnljSFFpMmtfZjBwLWFrRUlWeGQtLTcxZUtQZXFpdFJhaUtOV1FmTk5oejZVODd1NGw4N0E5R1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5BeUpHVFo4MTVMTGVWV2ZPMGhkVWlMcUZSWV9QeVV5Tkt5OXB1NDh1dkl1M01zUTV4QXhINk1EZk9JMlg0eU1pR2YwSlN6UlgwazV2dm8wXzZWbDBlQXFhZVp3cVhLRS1UQ2VJ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2087,71 +2087,71 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>미·중 정상회담 D-1…"반도체 규제 완화시 韓메모리 부정적" - 연합뉴스</t>
+          <t>인천FTA통상진흥센터, 화장품 수출기업 원산지관리 지원 - 기호일보</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>미·중 정상회담 D-1…"반도체 규제 완화시 韓메모리 부정적"&amp;nbsp;&amp;nbsp;연합뉴스</t>
+          <t>인천FTA통상진흥센터, 화장품 수출기업 원산지관리 지원&amp;nbsp;&amp;nbsp;기호일보</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 05:26:30 GMT</t>
+          <t>Wed, 13 May 2026 19:15:59 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5jeS1IZHNyUEJfd0dBRF9pSjBheUZDXzJjX0ppa0o2SjlZckhxUlJOVTQ5anFPcDc1RXJnX19BSGNDTVVwZ2ROSEdfYTBTcjhQWjJuaEo4Rm1sN3fSAWBBVV95cUxNT3Q4MDUzWUxBVTFWdWp4TEd0dFBpeVBBZDk0QklNVmVZZlZfYnlMbXVHMFRJYm9uTy1IVnJMQ3ZJNzIycDFqalZBU0pxY19HU2VIOExKOV9WalB6LThkY1Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE02QW9zMEhIcFZiZHh1VVVRbWRocGtnY1Fob1BlSkJ0anN0Y0xJeGFpQ0tTYng3VFJvaGU4S0hjTmxjV093dnBhMjBVSHI2Q2lyN3BHb0k5NTczQ0Myc2E2VVI0bm5GMlo0WlVqaEJpRQ?oc=5</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>'세기의 담판'에 젠슨 황 합류…AI 칩, 협상 테이블 핵심 의제로 - 이데일리</t>
+          <t>목포상공회의소, 수출기업 대상 FTA·무역증명 실무교육 실시 - 웹이코노미</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>'세기의 담판'에 젠슨 황 합류…AI 칩, 협상 테이블 핵심 의제로&amp;nbsp;&amp;nbsp;이데일리</t>
+          <t>목포상공회의소, 수출기업 대상 FTA·무역증명 실무교육 실시&amp;nbsp;&amp;nbsp;웹이코노미</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 09:50:07 GMT</t>
+          <t>Thu, 14 May 2026 11:56:10 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmVEdXluTXN5bS1DR0NUcXQwaHcxbnpyX2p1Y2hxSUliNVRzRjdrNWE5SVl5WmhfZ3BVM05SNV90aGpUdzAxU3h3bmRINXItZzZZUFFVTXlHMW1TYVgtZUFpcWtEOEJsNXg3UUN0TVdrUnU1STZIeTE0N1B6RzlkQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1LVjNBSGhYYjVUNG5FUFhvYXlKYlBYQ29IbFl4RE5QYTJOYmRCSE5jQkFtR21TZ3NmekowUDl1emRCR1o4MG5TY3FTVG9WeERmSzFhNVFMdkNJTTZZNS1wVW9rSGczTzc4ck5oZllUQnJRUQ?oc=5</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2161,34 +2161,34 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>"희토류 틀어쥔 중국"…'공급망 리스크' 고조[미중정상회담 D-1] - newsis.com</t>
+          <t>[날씨]강원산지 14일 짙은 안개⋯한낮 초여름 더위 - 강원일보</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>"희토류 틀어쥔 중국"…'공급망 리스크' 고조[미중정상회담 D-1]&amp;nbsp;&amp;nbsp;newsis.com</t>
+          <t>[날씨]강원산지 14일 짙은 안개⋯한낮 초여름 더위&amp;nbsp;&amp;nbsp;강원일보</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:26:19 GMT</t>
+          <t>Thu, 14 May 2026 00:25:10 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBRS2pvcjkyWlR3TVJUTktfZlZoOUNRMGUwU1hLdVNBWWlhSmRORXdzWGtVNDRmMHRoaE5feE5yakJCWlY2RVEta0Zqemd0MDRjRDF2M0xVYjlDcGM0aHFUOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9LY1RQWHJHTUFwREZSVGhtVHJjZFVLNE5FalZYdGlVcVg1WFJqMno4ZFNCNVZPSklJRk9HR2V0aHpvZVl5NFVFcWJCWC1HekJZbFNHbVNqbW9QakR3aDByUFl6Si0?oc=5</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2198,34 +2198,34 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>법무법인 율촌, K방산 글로벌 진출 전략 세미나 개최 - 한국경제</t>
+          <t>목포상의, FTA·무역증명 실무역량 강화 지원 - 전남투데이</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>법무법인 율촌, K방산 글로벌 진출 전략 세미나 개최&amp;nbsp;&amp;nbsp;한국경제</t>
+          <t>목포상의, FTA·무역증명 실무역량 강화 지원&amp;nbsp;&amp;nbsp;전남투데이</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 06:20:36 GMT</t>
+          <t>Thu, 14 May 2026 09:50:08 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBjdVVhNmQ0S0RrME5YbGo3YVdJUkZETkxQXzRWSkhoRHlPdzVPVC1VT0c3eWZHQUFtSkctSmI3ZWpJbkpRNWdQNUVhZDc3bGpjWHIzSFRjVmttd9IBVEFVX3lxTE04VlhIekVHdHJ4Vzl2cDZ5RW5MbW1VMjhaSEUzMU90RU51bkJHVExxSzZ6QzVxUC1FblFBWUZnNzE5Qk9rckpwSUJ1LXF6TlJ5Z3FpRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE51ZWRHRTlRMVBWbWY2bWdkZk5YaFhCWFVYVEtmclV4UEZkQ01RRDI5RWVMa3h1bmQxa0REMEsxZnFac2dMbV91UEhrVWFtRTlaRVFobTJuQ1lESXhOSWFmZHBjTQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2235,9 +2235,342 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>[게시판] 산업부·무역안보관리원, 캄보디아에 수출통제 노하우 전수 - 연합뉴스 한민족센터</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[게시판] 산업부·무역안보관리원, 캄보디아에 수출통제 노하우 전수&amp;nbsp;&amp;nbsp;연합뉴스 한민족센터</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 05:40:31 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBPbXR2bzM0MjU1VzFWQ2MtNXVHNHI2eWNJTm5pck1wSmRYbnlZWTZxczZncGhLbG9RY0psOGJvbDNZaEtocG52Yi1RYk11c2toRlZpWEVZSmRDZDJXanREcjAwbXZVVUZXLTF4Y3VueTBMZ1Zv?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[게시판] 산업부·무역안보관리원, 캄보디아에 수출통제 노하우 전수 - 연합뉴스</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[게시판] 산업부·무역안보관리원, 캄보디아에 수출통제 노하우 전수&amp;nbsp;&amp;nbsp;연합뉴스</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 05:40:31 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE41U3pGbnpHMWFKdzlHbnlhMDdZTFp5cnV3bmNoeDFDaUplR0x1eG1pZE00SmkzRVpzZDJMXzZFT2NBX3hqRzZxR0gzU1g0N051Mkd3WGhWTWk2YlnSAWBBVV95cUxOb3h5a2pKZVRJb090M0RaeE5FaFlFMktNZ2JhT2lxVmZRZGZxUldnRVgzV3dTQURsSWRWb2pzUElzWXpSdEJJRVpoZWRtVHZjbUxLMG9wMUhtamVxY0cwa2Y?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>엔비디아 중국 수출 활로 열리나…`젠슨 황` 美·中 `AI칩 수출 규제` 협상 카드 부상 - 디지털데일리</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>엔비디아 중국 수출 활로 열리나…`젠슨 황` 美·中 `AI칩 수출 규제` 협상 카드 부상&amp;nbsp;&amp;nbsp;디지털데일리</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 01:08:20 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBkc25jeGRFaU1GaVFEZVk4aHRmV3pMR0VYS2VrQTFHVDlPUnNrUXhEazFLNmNJVWRvRW0xNEVCN2htT2xUQWcxQkdaZ2pXM0dla1NXRHluOUlOTjVXclpVTmV6bnI?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
         <v>2</v>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>트럼프-시진핑 회담에서 희토류 수출 완화 논의..."중국 영향력 여전해" - 더구루</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>트럼프-시진핑 회담에서 희토류 수출 완화 논의..."중국 영향력 여전해"&amp;nbsp;&amp;nbsp;더구루</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 00:40:13 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5Uam9zdnVUTWhUNE9rRTZhSDQwSkRYLVpoaS1KQ2pjdzgzNWpMRlFtVzV0UU11a3o1MnViT1dpWl9SSXRDZkhZeWlWbE1aUnR3VnVTN1BoaUFZV2tzZGlFOTN2MA?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>한-베 수출통제 협력 국장급 채널 만든다..베트남 정부, 한·베 수출통제 협력 MOU 내용 공개 - 파이낸셜뉴스</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한-베 수출통제 협력 국장급 채널 만든다..베트남 정부, 한·베 수출통제 협력 MOU 내용 공개&amp;nbsp;&amp;nbsp;파이낸셜뉴스</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 04:27:01 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lb0ViaDI4YjNyZjJSMW9SeWdMMDdaUE1vQ2lTTmlxdFhSZHg3eHdPb3RjZFNPeTJxZFpKSWlkQjVjcE45R193VVFnWVFnV1ZvTGM2V05lMEh1QdIBXkFVX3lxTFBray13SkZuWXVYUmdsYkROTzQyNnJGS1ZPQXJzNkxQTEZtbndaNV9VQkFrLWFPeUdlVnVLZ3ZjaVhnMzFMZmh3MVByVnNyMUoxS1hJQVd0SVNnNUtDMGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>미·중 정상회담에 반도체주 촉각··희토류 공급우위 중국에 수출규제 완화? - 동양뉴스</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>미·중 정상회담에 반도체주 촉각··희토류 공급우위 중국에 수출규제 완화?&amp;nbsp;&amp;nbsp;동양뉴스</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 00:42:50 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5aUUFYZzBIZ0Y1eUJfa1p1emRtaDRScXhCczdabXAwX3BCN3JCdjY3MDlCcE1QbEJNQU42SEU0REs2OU0yOWRJWDJsajlxWnVGWXBzaTUxVzhHYkVUUzAzTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>[게시판] 산업부·무역안보관리원, 캄보디아에 수출통제 노하우 전수 - 네이트</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[게시판] 산업부·무역안보관리원, 캄보디아에 수출통제 노하우 전수&amp;nbsp;&amp;nbsp;네이트</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 05:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE54VFRRTjFWb29uYXpjdl9zWmx0aE9kQ3FyQ0wzOXAxcDlHaFpUWUNpWTN3d3M4bUEtVWZvbGliTmFXaW90UWE5M3hNaDVCSnNTS0tj?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>희토류 카드 쥔 중국…미·중 정상회담에 반도체株 촉각 - 뉴시스</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>희토류 카드 쥔 중국…미·중 정상회담에 반도체株 촉각&amp;nbsp;&amp;nbsp;뉴시스</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBSeVdmU2dhNWxzRnRObGkxczAzMkJaWTB5RTg5NTdNUFA5MHJmc0hyb1NKYVBSZ1Q1Vm4tSWU0TVZydmNlTDBZT1hQdnlreFRpVC1kVjRfbzN2T3l6ZGo1dtIBeEFVX3lxTE9veXFVZDIxT1dNa0pOUEwtcmlBaGlnLVBUT2J1UElzUFkySzBEMDJLRVF6OV92Y19YUHVuS0RrVy0yZzFQMXA0aFlEQjdweFNULXI1N2h1YnVlaEdNU2tZQS1CWUh4WUJESkpwSU51X0d2alRaTVZGWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>미중 회담서 논의될 반도체, 삼전닉스에 득일까 실일까 - 노컷뉴스</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>미중 회담서 논의될 반도체, 삼전닉스에 득일까 실일까&amp;nbsp;&amp;nbsp;노컷뉴스</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE44b0ZmRzRvY0hmSDdiX2UtUFJtdnljSFFpMmtfZjBwLWFrRUlWeGQtLTcxZUtQZXFpdFJhaUtOV1FmTk5oejZVODd1NGw4N0E5R1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
